--- a/Analysis/raw data/Survey 2 clean_near complete_16.6.26.xlsx
+++ b/Analysis/raw data/Survey 2 clean_near complete_16.6.26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ranidavis/Desktop/Bats &amp; agriculture/Beneficial Bats - collaborative paper/IBRC paper analysis/IBRC beneficial bats survey response analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ranidavis/Desktop/Bats &amp; agriculture/Beneficial Bats - collaborative paper/IBRC paper analysis/IBRC beneficial bats survey response analysis/Analysis/raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{D8DD9238-A5A3-474D-B665-0CBF26E006E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1CBA14-48CF-364E-89EC-60A28A70DFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-2100" windowWidth="28640" windowHeight="19400"/>
+    <workbookView xWindow="-38400" yWindow="-2100" windowWidth="28640" windowHeight="19400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Survey 2_near complete_16.6.26" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="505">
   <si>
     <t>Status</t>
   </si>
@@ -709,9 +709,6 @@
     <t>Many artificial water sources- I don't think any have been developed for biodiversity benefit but certainly attract birds etc.</t>
   </si>
   <si>
-    <t>Nayelli Rivera</t>
-  </si>
-  <si>
     <t>Nayelli Rivera, a.riveravillanueva@student.uq.edu.au</t>
   </si>
   <si>
@@ -975,9 +972,6 @@
     <t>Crop.type.clean</t>
   </si>
   <si>
-    <t>Adrià López-Baucells</t>
-  </si>
-  <si>
     <t>R1</t>
   </si>
   <si>
@@ -996,9 +990,6 @@
     <t>Vegetable crops</t>
   </si>
   <si>
-    <t>Alexandra Howard</t>
-  </si>
-  <si>
     <t>R2</t>
   </si>
   <si>
@@ -1014,9 +1005,6 @@
     <t>Perennial fruit crops</t>
   </si>
   <si>
-    <t>Andrés Muñoz-Sáez</t>
-  </si>
-  <si>
     <t>R3</t>
   </si>
   <si>
@@ -1032,9 +1020,6 @@
     <t>Vineyard</t>
   </si>
   <si>
-    <t>April Reside</t>
-  </si>
-  <si>
     <t>R4</t>
   </si>
   <si>
@@ -1053,9 +1038,6 @@
     <t>Mixed farming system</t>
   </si>
   <si>
-    <t>Ara Monadjem</t>
-  </si>
-  <si>
     <t>R5</t>
   </si>
   <si>
@@ -1071,9 +1053,6 @@
     <t>Field crops</t>
   </si>
   <si>
-    <t>Brooke Maslo</t>
-  </si>
-  <si>
     <t>R6</t>
   </si>
   <si>
@@ -1089,9 +1068,6 @@
     <t>Multi- fruit &amp; orchard</t>
   </si>
   <si>
-    <t>Carme Tuneu-Corral</t>
-  </si>
-  <si>
     <t>R7</t>
   </si>
   <si>
@@ -1110,9 +1086,6 @@
     <t>Madagascar</t>
   </si>
   <si>
-    <t>Carmi Korine</t>
-  </si>
-  <si>
     <t>R8</t>
   </si>
   <si>
@@ -1158,9 +1131,6 @@
     <t>UnspCentral Districts</t>
   </si>
   <si>
-    <t>Cárol Sierra-Durán</t>
-  </si>
-  <si>
     <t>R9</t>
   </si>
   <si>
@@ -1173,9 +1143,6 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Carolina Ocampo-Ariza</t>
-  </si>
-  <si>
     <t>R10</t>
   </si>
   <si>
@@ -1188,9 +1155,6 @@
     <t>Agroforestry cacao</t>
   </si>
   <si>
-    <t>Cecilia Montauban</t>
-  </si>
-  <si>
     <t>R11</t>
   </si>
   <si>
@@ -1203,9 +1167,6 @@
     <t>Multi- crop</t>
   </si>
   <si>
-    <t>Danilo Russo</t>
-  </si>
-  <si>
     <t>R12</t>
   </si>
   <si>
@@ -1215,9 +1176,6 @@
     <t>Italy</t>
   </si>
   <si>
-    <t>Diogo Ferreira</t>
-  </si>
-  <si>
     <t>R13</t>
   </si>
   <si>
@@ -1230,9 +1188,6 @@
     <t>1 &amp; 2</t>
   </si>
   <si>
-    <t>Kadambari Deshpande</t>
-  </si>
-  <si>
     <t>R14</t>
   </si>
   <si>
@@ -1245,9 +1200,6 @@
     <t>South Asia</t>
   </si>
   <si>
-    <t>Elisa Fuentes-Montemayor</t>
-  </si>
-  <si>
     <t>R15</t>
   </si>
   <si>
@@ -1260,9 +1212,6 @@
     <t>Multi- crop &amp; pasture</t>
   </si>
   <si>
-    <t>Florence Matutini</t>
-  </si>
-  <si>
     <t>R16</t>
   </si>
   <si>
@@ -1287,9 +1236,6 @@
     <t>Pecan</t>
   </si>
   <si>
-    <t>Heidi Kolkert</t>
-  </si>
-  <si>
     <t>R18</t>
   </si>
   <si>
@@ -1299,9 +1245,6 @@
     <t>Blueberries</t>
   </si>
   <si>
-    <t>Hugo Rebelo</t>
-  </si>
-  <si>
     <t>R19</t>
   </si>
   <si>
@@ -1320,9 +1263,6 @@
     <t>Forestry</t>
   </si>
   <si>
-    <t>Hui Wu</t>
-  </si>
-  <si>
     <t>R20</t>
   </si>
   <si>
@@ -1335,27 +1275,18 @@
     <t>East Asia</t>
   </si>
   <si>
-    <t>Jarod McTaggart</t>
-  </si>
-  <si>
     <t>R21</t>
   </si>
   <si>
     <t>Auckland</t>
   </si>
   <si>
-    <t>Jeremy Froidevaux</t>
-  </si>
-  <si>
     <t>R22</t>
   </si>
   <si>
     <t>Bourgogne-Franche-Comté</t>
   </si>
   <si>
-    <t>Jérémy Froidevaux</t>
-  </si>
-  <si>
     <t>R23</t>
   </si>
   <si>
@@ -1371,15 +1302,9 @@
     <t>Taiwan</t>
   </si>
   <si>
-    <t>José M. Herrera</t>
-  </si>
-  <si>
     <t>R25</t>
   </si>
   <si>
-    <t>Leonardo Ancillotto</t>
-  </si>
-  <si>
     <t>R26</t>
   </si>
   <si>
@@ -1389,9 +1314,6 @@
     <t>Lazio</t>
   </si>
   <si>
-    <t>Maggie Campbell-Jones</t>
-  </si>
-  <si>
     <t>R28</t>
   </si>
   <si>
@@ -1401,9 +1323,6 @@
     <t>Zacatecas</t>
   </si>
   <si>
-    <t>Peter Taylor</t>
-  </si>
-  <si>
     <t>R30</t>
   </si>
   <si>
@@ -1416,15 +1335,9 @@
     <t>Macadamia</t>
   </si>
   <si>
-    <t>Rani Davis</t>
-  </si>
-  <si>
     <t>R31</t>
   </si>
   <si>
-    <t>Sándor Zsebők</t>
-  </si>
-  <si>
     <t>R32</t>
   </si>
   <si>
@@ -1434,9 +1347,6 @@
     <t>Hungary</t>
   </si>
   <si>
-    <t>Siteri Tikoca</t>
-  </si>
-  <si>
     <t>R33</t>
   </si>
   <si>
@@ -1446,9 +1356,6 @@
     <t>Fiji</t>
   </si>
   <si>
-    <t>Stuart Parsons</t>
-  </si>
-  <si>
     <t>R34</t>
   </si>
   <si>
@@ -1458,9 +1365,6 @@
     <t>Australia &amp; New Zealand</t>
   </si>
   <si>
-    <t>Teja Tscharntke</t>
-  </si>
-  <si>
     <t>R35</t>
   </si>
   <si>
@@ -1488,15 +1392,9 @@
     <t>Multi-region: Jilin province, yunnan province, henan province, shandong provinc &amp; shanxi province</t>
   </si>
   <si>
-    <t>Xavier Puig-Montserrat</t>
-  </si>
-  <si>
     <t>R37</t>
   </si>
   <si>
-    <t>Zenon Czenze &amp; Heidi Kolkert</t>
-  </si>
-  <si>
     <t>R38</t>
   </si>
   <si>
@@ -1506,46 +1404,151 @@
     <t>Chiara Paniccia &lt;chiara.paniccia@eurac.edu&gt;</t>
   </si>
   <si>
-    <t>Helen Taylor-Boyd</t>
-  </si>
-  <si>
     <t>R39</t>
   </si>
   <si>
-    <t>Yingying Liu</t>
-  </si>
-  <si>
     <t>R40</t>
   </si>
   <si>
-    <t>Bea Maas</t>
-  </si>
-  <si>
     <t>R41</t>
   </si>
   <si>
-    <t>Olga Heim</t>
-  </si>
-  <si>
     <t>R42</t>
   </si>
   <si>
-    <t>Kirsten Reichel-Jung</t>
-  </si>
-  <si>
     <t>R43</t>
   </si>
   <si>
-    <t>Chiara Paniccia</t>
-  </si>
-  <si>
     <t>R44</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>AH</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>BM</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>CK</t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>CM</t>
+  </si>
+  <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>DF</t>
+  </si>
+  <si>
+    <t>KD</t>
+  </si>
+  <si>
+    <t>EF</t>
+  </si>
+  <si>
+    <t>FM</t>
+  </si>
+  <si>
+    <t>GM</t>
+  </si>
+  <si>
+    <t>HK</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>HW</t>
+  </si>
+  <si>
+    <t>JM</t>
+  </si>
+  <si>
+    <t>JF</t>
+  </si>
+  <si>
+    <t>JN</t>
+  </si>
+  <si>
+    <t>JH</t>
+  </si>
+  <si>
+    <t>LA</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>RD</t>
+  </si>
+  <si>
+    <t>SZ</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>TJ</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>ZC &amp; HK</t>
+  </si>
+  <si>
+    <t>HT</t>
+  </si>
+  <si>
+    <t>YL</t>
+  </si>
+  <si>
+    <t>OH</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>CP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -2151,7 +2154,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2180,23 +2183,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2207,10 +2201,10 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="42" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2268,7 +2262,7 @@
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="42"/>
+    <cellStyle name="Normal 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
@@ -2289,9 +2283,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2329,7 +2323,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2435,7 +2429,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2577,23 +2571,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="9"/>
-    <col min="2" max="2" width="22.1640625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="14.1640625" style="10" customWidth="1"/>
-    <col min="4" max="5" width="19.33203125" style="10" customWidth="1"/>
-    <col min="6" max="6" width="17.1640625" style="10" customWidth="1"/>
-    <col min="7" max="9" width="19.33203125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" style="9" customWidth="1"/>
+    <col min="4" max="5" width="19.33203125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="17.1640625" style="9" customWidth="1"/>
+    <col min="7" max="9" width="19.33203125" style="9" customWidth="1"/>
     <col min="10" max="23" width="34.33203125" style="9" customWidth="1"/>
     <col min="24" max="24" width="28" style="9" customWidth="1"/>
     <col min="25" max="16384" width="10.83203125" style="9"/>
@@ -2604,28 +2598,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>1</v>
@@ -2675,28 +2669,28 @@
         <v>15</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>315</v>
+        <v>464</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D2" s="7">
         <v>1</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>319</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>321</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>16</v>
@@ -2743,28 +2737,28 @@
         <v>15</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>322</v>
+        <v>465</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D3" s="8">
         <v>1</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>84</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>29</v>
@@ -2799,28 +2793,28 @@
         <v>15</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>328</v>
+        <v>466</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D4" s="8">
         <v>1</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>36</v>
@@ -2858,28 +2852,28 @@
         <v>15</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>334</v>
+        <v>467</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D5" s="8">
         <v>1</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>42</v>
@@ -2929,28 +2923,28 @@
         <v>15</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>341</v>
+        <v>468</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D6" s="8">
         <v>1</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>51</v>
@@ -2991,28 +2985,28 @@
         <v>15</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>347</v>
+        <v>469</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D7" s="8">
         <v>1</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>57</v>
@@ -3059,28 +3053,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>353</v>
+        <v>470</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D8" s="8">
         <v>2</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>64</v>
@@ -3121,28 +3115,28 @@
         <v>15</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>353</v>
+        <v>470</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D9" s="8">
         <v>1</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>70</v>
@@ -3177,28 +3171,28 @@
         <v>15</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>360</v>
+        <v>471</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D10" s="8">
         <v>9</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>213</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>73</v>
@@ -3233,28 +3227,28 @@
         <v>15</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>360</v>
+        <v>471</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D11" s="8">
         <v>1</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>73</v>
@@ -3301,28 +3295,28 @@
         <v>15</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>360</v>
+        <v>471</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>84</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>73</v>
@@ -3366,28 +3360,28 @@
         <v>15</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="E13" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>370</v>
-      </c>
       <c r="F13" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>89</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>73</v>
@@ -3434,28 +3428,28 @@
         <v>15</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>360</v>
+        <v>471</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>371</v>
+        <v>352</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>362</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>73</v>
@@ -3499,28 +3493,28 @@
         <v>15</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>360</v>
+        <v>471</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>371</v>
+        <v>352</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>362</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>73</v>
@@ -3555,28 +3549,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>360</v>
+        <v>471</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D16" s="8">
         <v>21</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>373</v>
-      </c>
       <c r="I16" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>73</v>
@@ -3620,28 +3614,28 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>360</v>
+        <v>471</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D17" s="8">
         <v>2</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>104</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>73</v>
@@ -3685,28 +3679,28 @@
         <v>15</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>360</v>
+        <v>471</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D18" s="8">
         <v>16</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>73</v>
@@ -3753,28 +3747,28 @@
         <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>360</v>
+        <v>471</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D19" s="8">
         <v>3</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>106</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>73</v>
@@ -3824,28 +3818,28 @@
         <v>15</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>360</v>
+        <v>471</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>371</v>
+        <v>352</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>362</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>73</v>
@@ -3880,28 +3874,28 @@
         <v>15</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>376</v>
+        <v>472</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="D21" s="8">
         <v>2</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="F21" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="H21" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="I21" s="6" t="s">
         <v>319</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>321</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>112</v>
@@ -3942,28 +3936,28 @@
         <v>15</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>376</v>
+        <v>472</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="D22" s="8">
         <v>1</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>112</v>
@@ -4004,28 +3998,28 @@
         <v>15</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>381</v>
+        <v>473</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="D23" s="8">
         <v>1</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>122</v>
@@ -4057,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>386</v>
+        <v>474</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="D24" s="8">
         <v>1</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>124</v>
@@ -4116,28 +4110,28 @@
         <v>15</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>391</v>
+        <v>475</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="D25" s="8">
         <v>1</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>84</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>128</v>
@@ -4172,28 +4166,28 @@
         <v>15</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>133</v>
@@ -4234,28 +4228,28 @@
         <v>15</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>400</v>
+        <v>477</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="D27" s="8">
         <v>1</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>138</v>
@@ -4296,28 +4290,28 @@
         <v>15</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>405</v>
+        <v>478</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="D28" s="7">
         <v>3</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>143</v>
@@ -4367,28 +4361,28 @@
         <v>15</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>410</v>
+        <v>479</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D29" s="7">
         <v>1</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>151</v>
@@ -4420,28 +4414,28 @@
         <v>15</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>410</v>
+        <v>479</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D30" s="7">
         <v>2</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>151</v>
@@ -4476,28 +4470,28 @@
         <v>15</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>410</v>
+        <v>479</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D31" s="7">
         <v>3</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>84</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>151</v>
@@ -4529,28 +4523,28 @@
         <v>15</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>155</v>
+        <v>480</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="D32" s="7">
         <v>1</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>89</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="J32" s="9" t="s">
         <v>155</v>
@@ -4594,28 +4588,28 @@
         <v>15</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>155</v>
+        <v>480</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="D33" s="7">
         <v>2</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>155</v>
@@ -4656,28 +4650,28 @@
         <v>15</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>419</v>
+        <v>481</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="D34" s="8">
         <v>1</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>89</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>165</v>
@@ -4724,28 +4718,28 @@
         <v>15</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>419</v>
+        <v>481</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="D35" s="8">
         <v>2</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>165</v>
@@ -4795,28 +4789,28 @@
         <v>15</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>423</v>
+        <v>482</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="D36" s="7">
         <v>1</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>425</v>
+        <v>406</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>179</v>
@@ -4860,28 +4854,28 @@
         <v>15</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>423</v>
+        <v>482</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="D37" s="7">
         <v>2</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>179</v>
@@ -4916,28 +4910,28 @@
         <v>15</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>430</v>
+        <v>483</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="D38" s="8">
         <v>1</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>84</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J38" s="9" t="s">
         <v>186</v>
@@ -4972,28 +4966,28 @@
         <v>15</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>435</v>
+        <v>484</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="D39" s="8">
         <v>1</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>437</v>
+        <v>416</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>190</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>189</v>
@@ -5037,28 +5031,28 @@
         <v>15</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>438</v>
+        <v>485</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>439</v>
+        <v>417</v>
       </c>
       <c r="D40" s="8">
         <v>1</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J40" s="9" t="s">
         <v>195</v>
@@ -5099,28 +5093,28 @@
         <v>15</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>441</v>
+        <v>485</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="D41" s="8">
         <v>2</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>201</v>
@@ -5170,28 +5164,28 @@
         <v>15</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>209</v>
+        <v>486</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>444</v>
+        <v>421</v>
       </c>
       <c r="D42" s="8">
         <v>1</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>446</v>
+        <v>423</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="J42" s="9" t="s">
         <v>209</v>
@@ -5225,29 +5219,29 @@
       <c r="A43" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="14" t="s">
-        <v>447</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>448</v>
-      </c>
-      <c r="D43" s="15">
+      <c r="B43" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="D43" s="7">
         <v>1</v>
       </c>
-      <c r="E43" s="14" t="s">
-        <v>425</v>
-      </c>
-      <c r="F43" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="G43" s="14" t="s">
-        <v>319</v>
-      </c>
-      <c r="H43" s="14" t="s">
+      <c r="E43" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="H43" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="I43" s="14" t="s">
-        <v>327</v>
+      <c r="I43" s="6" t="s">
+        <v>324</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>212</v>
@@ -5282,28 +5276,28 @@
         <v>15</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>449</v>
+        <v>488</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="D44" s="7">
         <v>1</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>213</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J44" s="9" t="s">
         <v>215</v>
@@ -5338,28 +5332,28 @@
         <v>15</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>449</v>
+        <v>488</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="D45" s="7">
         <v>2</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>215</v>
@@ -5394,28 +5388,28 @@
         <v>15</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>453</v>
+        <v>489</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="D46" s="8">
         <v>1</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>89</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="J46" s="9" t="s">
         <v>220</v>
@@ -5462,70 +5456,70 @@
         <v>15</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>227</v>
+        <v>490</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>455</v>
+        <v>429</v>
       </c>
       <c r="D47" s="8">
         <v>1</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J47" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="K47" s="9" t="s">
         <v>228</v>
-      </c>
-      <c r="K47" s="9" t="s">
-        <v>229</v>
       </c>
       <c r="L47" s="9" t="s">
         <v>31</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N47" s="9" t="s">
         <v>33</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>22</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="R47" s="9" t="s">
         <v>24</v>
       </c>
       <c r="S47" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="T47" s="9" t="s">
         <v>41</v>
       </c>
       <c r="U47" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="V47" s="9" t="s">
         <v>28</v>
       </c>
       <c r="W47" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5533,34 +5527,34 @@
         <v>15</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="D48" s="8">
         <v>1</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>459</v>
+        <v>432</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>460</v>
+        <v>433</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J48" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="K48" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="K48" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="L48" s="9" t="s">
         <v>31</v>
@@ -5586,46 +5580,46 @@
         <v>15</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="D49" s="8">
         <v>2</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>459</v>
+        <v>432</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>461</v>
+        <v>434</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L49" s="9" t="s">
         <v>18</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N49" s="9" t="s">
         <v>33</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>34</v>
@@ -5634,7 +5628,7 @@
         <v>24</v>
       </c>
       <c r="S49" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="T49" s="9" t="s">
         <v>41</v>
@@ -5648,70 +5642,70 @@
         <v>15</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>463</v>
+        <v>435</v>
       </c>
       <c r="D50" s="8">
         <v>1</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>461</v>
+        <v>434</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J50" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="K50" s="9" t="s">
         <v>242</v>
-      </c>
-      <c r="K50" s="9" t="s">
-        <v>243</v>
       </c>
       <c r="L50" s="9" t="s">
         <v>53</v>
       </c>
       <c r="M50" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N50" s="9" t="s">
         <v>33</v>
       </c>
       <c r="O50" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P50" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q50" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="R50" s="9" t="s">
         <v>24</v>
       </c>
       <c r="S50" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="T50" s="9" t="s">
         <v>41</v>
       </c>
       <c r="U50" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="V50" s="9" t="s">
         <v>28</v>
       </c>
       <c r="W50" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5719,34 +5713,34 @@
         <v>15</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>464</v>
+        <v>493</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="D51" s="7">
         <v>1</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J51" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="K51" s="9" t="s">
         <v>250</v>
-      </c>
-      <c r="K51" s="9" t="s">
-        <v>251</v>
       </c>
       <c r="L51" s="9" t="s">
         <v>53</v>
@@ -5755,7 +5749,7 @@
         <v>129</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>34</v>
@@ -5775,70 +5769,70 @@
         <v>15</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>468</v>
+        <v>494</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="D52" s="8">
         <v>1</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J52" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="K52" s="9" t="s">
         <v>253</v>
-      </c>
-      <c r="K52" s="9" t="s">
-        <v>254</v>
       </c>
       <c r="L52" s="9" t="s">
         <v>53</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N52" s="9" t="s">
         <v>33</v>
       </c>
       <c r="O52" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P52" s="9" t="s">
         <v>22</v>
       </c>
       <c r="Q52" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R52" s="9" t="s">
         <v>61</v>
       </c>
       <c r="S52" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T52" s="9" t="s">
         <v>41</v>
       </c>
       <c r="U52" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V52" s="9" t="s">
         <v>28</v>
       </c>
       <c r="W52" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="53" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5846,70 +5840,70 @@
         <v>15</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="D53" s="8">
         <v>1</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>474</v>
+        <v>443</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J53" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="K53" s="9" t="s">
         <v>261</v>
-      </c>
-      <c r="K53" s="9" t="s">
-        <v>262</v>
       </c>
       <c r="L53" s="9" t="s">
         <v>53</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N53" s="9" t="s">
         <v>33</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q53" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="R53" s="9" t="s">
         <v>131</v>
       </c>
       <c r="S53" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T53" s="9" t="s">
         <v>41</v>
       </c>
       <c r="U53" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="V53" s="9" t="s">
         <v>28</v>
       </c>
       <c r="W53" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="54" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5917,34 +5911,34 @@
         <v>15</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>477</v>
+        <v>445</v>
       </c>
       <c r="D54" s="8">
         <v>2</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>482</v>
+        <v>450</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="J54" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="K54" s="9" t="s">
         <v>269</v>
-      </c>
-      <c r="K54" s="9" t="s">
-        <v>270</v>
       </c>
       <c r="L54" s="9" t="s">
         <v>53</v>
@@ -5953,19 +5947,19 @@
         <v>129</v>
       </c>
       <c r="O54" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P54" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q54" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="R54" s="9" t="s">
         <v>61</v>
       </c>
       <c r="S54" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="T54" s="9" t="s">
         <v>41</v>
@@ -5979,34 +5973,34 @@
         <v>15</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>477</v>
+        <v>445</v>
       </c>
       <c r="D55" s="8">
         <v>3</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>481</v>
+        <v>449</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>461</v>
+        <v>434</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L55" s="9" t="s">
         <v>31</v>
@@ -6032,34 +6026,34 @@
         <v>15</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>477</v>
+        <v>445</v>
       </c>
       <c r="D56" s="8">
         <v>1</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>478</v>
+        <v>446</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>479</v>
+        <v>447</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L56" s="9" t="s">
         <v>53</v>
@@ -6071,7 +6065,7 @@
         <v>34</v>
       </c>
       <c r="Q56" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R56" s="9" t="s">
         <v>24</v>
@@ -6088,34 +6082,34 @@
         <v>15</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>277</v>
+        <v>497</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>484</v>
+        <v>452</v>
       </c>
       <c r="D57" s="8">
         <v>1</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>485</v>
+        <v>453</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J57" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="K57" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="K57" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="L57" s="9" t="s">
         <v>18</v>
@@ -6141,58 +6135,58 @@
         <v>15</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>487</v>
+        <v>454</v>
       </c>
       <c r="D58" s="7">
         <v>1</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G58" s="6" t="s">
         <v>317</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>319</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>213</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J58" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="K58" s="9" t="s">
         <v>279</v>
-      </c>
-      <c r="K58" s="9" t="s">
-        <v>280</v>
       </c>
       <c r="L58" s="9" t="s">
         <v>18</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N58" s="9" t="s">
         <v>20</v>
       </c>
       <c r="O58" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P58" s="9" t="s">
         <v>147</v>
       </c>
       <c r="Q58" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="R58" s="9" t="s">
         <v>24</v>
       </c>
       <c r="S58" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="T58" s="9" t="s">
         <v>41</v>
@@ -6206,58 +6200,58 @@
         <v>15</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>487</v>
+        <v>454</v>
       </c>
       <c r="D59" s="7">
         <v>2</v>
       </c>
       <c r="E59" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G59" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="F59" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>319</v>
-      </c>
       <c r="H59" s="6" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L59" s="9" t="s">
         <v>18</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N59" s="9" t="s">
         <v>20</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q59" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="R59" s="9" t="s">
         <v>24</v>
       </c>
       <c r="S59" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="T59" s="9" t="s">
         <v>41</v>
@@ -6271,58 +6265,58 @@
         <v>15</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>487</v>
+        <v>454</v>
       </c>
       <c r="D60" s="7">
         <v>3</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>319</v>
-      </c>
       <c r="H60" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K60" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L60" s="9" t="s">
         <v>31</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N60" s="9" t="s">
         <v>20</v>
       </c>
       <c r="O60" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P60" s="9" t="s">
         <v>22</v>
       </c>
       <c r="Q60" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="R60" s="9" t="s">
         <v>24</v>
       </c>
       <c r="S60" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T60" s="9" t="s">
         <v>41</v>
@@ -6335,246 +6329,246 @@
       <c r="A61" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B61" s="16" t="s">
-        <v>488</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>489</v>
-      </c>
-      <c r="D61" s="17">
+      <c r="B61" s="13" t="s">
+        <v>499</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="D61" s="14">
         <v>1</v>
       </c>
-      <c r="E61" s="16" t="s">
-        <v>490</v>
-      </c>
-      <c r="F61" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="G61" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="H61" s="16" t="s">
+      <c r="E61" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="F61" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="G61" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="I61" s="16" t="s">
-        <v>333</v>
+      <c r="H61" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="I61" s="13" t="s">
+        <v>329</v>
       </c>
       <c r="J61" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="K61" s="9" t="s">
         <v>294</v>
-      </c>
-      <c r="K61" s="9" t="s">
-        <v>295</v>
       </c>
       <c r="L61" s="9" t="s">
         <v>53</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N61" s="9" t="s">
         <v>20</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>22</v>
       </c>
       <c r="Q61" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="R61" s="9" t="s">
         <v>24</v>
       </c>
       <c r="S61" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="T61" s="9" t="s">
         <v>41</v>
       </c>
       <c r="U61" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="V61" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="22" t="s">
+      <c r="A62" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>500</v>
+      </c>
+      <c r="C62" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="D62" s="17"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="16"/>
+      <c r="J62" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="B62" s="23" t="s">
-        <v>492</v>
-      </c>
-      <c r="C62" s="23" t="s">
-        <v>493</v>
-      </c>
-      <c r="D62" s="20"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="19"/>
-      <c r="J62" s="18" t="s">
+      <c r="K62" s="15"/>
+      <c r="L62" s="15"/>
+      <c r="M62" s="15"/>
+      <c r="N62" s="15"/>
+      <c r="O62" s="15"/>
+      <c r="P62" s="15"/>
+      <c r="Q62" s="15"/>
+      <c r="R62" s="15"/>
+      <c r="S62" s="15"/>
+      <c r="T62" s="15"/>
+      <c r="U62" s="15"/>
+      <c r="V62" s="15"/>
+    </row>
+    <row r="63" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D63" s="17"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="16"/>
+      <c r="H63" s="16"/>
+      <c r="I63" s="16"/>
+      <c r="J63" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="K62" s="18"/>
-      <c r="L62" s="18"/>
-      <c r="M62" s="18"/>
-      <c r="N62" s="18"/>
-      <c r="O62" s="18"/>
-      <c r="P62" s="18"/>
-      <c r="Q62" s="18"/>
-      <c r="R62" s="18"/>
-      <c r="S62" s="18"/>
-      <c r="T62" s="18"/>
-      <c r="U62" s="18"/>
-      <c r="V62" s="18"/>
-    </row>
-    <row r="63" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="24" t="s">
-        <v>301</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="C63" s="13" t="s">
-        <v>495</v>
-      </c>
-      <c r="D63" s="20"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="19"/>
-      <c r="J63" s="18" t="s">
+      <c r="K63" s="15"/>
+      <c r="L63" s="15"/>
+      <c r="M63" s="15"/>
+      <c r="N63" s="15"/>
+      <c r="O63" s="15"/>
+      <c r="P63" s="15"/>
+      <c r="Q63" s="15"/>
+      <c r="R63" s="15"/>
+      <c r="S63" s="15"/>
+      <c r="T63" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63" s="15"/>
+      <c r="V63" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="D64" s="17"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="16"/>
+      <c r="H64" s="16"/>
+      <c r="I64" s="16"/>
+      <c r="J64" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="K63" s="18"/>
-      <c r="L63" s="18"/>
-      <c r="M63" s="18"/>
-      <c r="N63" s="18"/>
-      <c r="O63" s="18"/>
-      <c r="P63" s="18"/>
-      <c r="Q63" s="18"/>
-      <c r="R63" s="18"/>
-      <c r="S63" s="18"/>
-      <c r="T63" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="U63" s="18"/>
-      <c r="V63" s="18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="64" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="24" t="s">
-        <v>301</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>497</v>
-      </c>
-      <c r="D64" s="20"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="18" t="s">
+      <c r="K64" s="15"/>
+      <c r="L64" s="15"/>
+      <c r="M64" s="15"/>
+      <c r="N64" s="15"/>
+      <c r="O64" s="15"/>
+      <c r="P64" s="15"/>
+      <c r="Q64" s="15"/>
+      <c r="R64" s="15"/>
+      <c r="S64" s="15"/>
+      <c r="T64" s="15"/>
+      <c r="U64" s="15"/>
+      <c r="V64" s="15"/>
+    </row>
+    <row r="65" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="D65" s="17"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="16"/>
+      <c r="H65" s="16"/>
+      <c r="I65" s="16"/>
+      <c r="J65" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="K64" s="18"/>
-      <c r="L64" s="18"/>
-      <c r="M64" s="18"/>
-      <c r="N64" s="18"/>
-      <c r="O64" s="18"/>
-      <c r="P64" s="18"/>
-      <c r="Q64" s="18"/>
-      <c r="R64" s="18"/>
-      <c r="S64" s="18"/>
-      <c r="T64" s="18"/>
-      <c r="U64" s="18"/>
-      <c r="V64" s="18"/>
-    </row>
-    <row r="65" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="24" t="s">
-        <v>301</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>498</v>
-      </c>
-      <c r="C65" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="D65" s="20"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="18" t="s">
+      <c r="K65" s="15"/>
+      <c r="L65" s="15"/>
+      <c r="M65" s="15"/>
+      <c r="N65" s="15"/>
+      <c r="O65" s="15"/>
+      <c r="P65" s="15"/>
+      <c r="Q65" s="15"/>
+      <c r="R65" s="15"/>
+      <c r="S65" s="15"/>
+      <c r="T65" s="15"/>
+      <c r="U65" s="15"/>
+      <c r="V65" s="15"/>
+    </row>
+    <row r="66" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="D66" s="17"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
+      <c r="H66" s="16"/>
+      <c r="I66" s="16"/>
+      <c r="J66" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="K65" s="18"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="18"/>
-      <c r="N65" s="18"/>
-      <c r="O65" s="18"/>
-      <c r="P65" s="18"/>
-      <c r="Q65" s="18"/>
-      <c r="R65" s="18"/>
-      <c r="S65" s="18"/>
-      <c r="T65" s="18"/>
-      <c r="U65" s="18"/>
-      <c r="V65" s="18"/>
-    </row>
-    <row r="66" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="B66" s="26" t="s">
-        <v>500</v>
-      </c>
-      <c r="C66" s="26" t="s">
-        <v>501</v>
-      </c>
-      <c r="D66" s="20"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="19"/>
-      <c r="J66" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="K66" s="18"/>
-      <c r="L66" s="18"/>
-      <c r="M66" s="18"/>
-      <c r="N66" s="18"/>
-      <c r="O66" s="18"/>
-      <c r="P66" s="18"/>
-      <c r="Q66" s="18"/>
-      <c r="R66" s="18"/>
-      <c r="S66" s="18"/>
-      <c r="T66" s="18"/>
-      <c r="U66" s="18"/>
-      <c r="V66" s="18"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="15"/>
+      <c r="M66" s="15"/>
+      <c r="N66" s="15"/>
+      <c r="O66" s="15"/>
+      <c r="P66" s="15"/>
+      <c r="Q66" s="15"/>
+      <c r="R66" s="15"/>
+      <c r="S66" s="15"/>
+      <c r="T66" s="15"/>
+      <c r="U66" s="15"/>
+      <c r="V66" s="15"/>
     </row>
     <row r="67" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="B67" s="21" t="s">
-        <v>502</v>
-      </c>
-      <c r="C67" s="13" t="s">
-        <v>503</v>
-      </c>
-      <c r="J67" s="21" t="s">
-        <v>491</v>
+      <c r="A67" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>504</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="J67" s="18" t="s">
+        <v>457</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis/raw data/Survey 2 clean_near complete_16.6.26.xlsx
+++ b/Analysis/raw data/Survey 2 clean_near complete_16.6.26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ranidavis/Desktop/Bats &amp; agriculture/Beneficial Bats - collaborative paper/IBRC paper analysis/IBRC beneficial bats survey response analysis/Analysis/raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1CBA14-48CF-364E-89EC-60A28A70DFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0E8B6B-88F0-1F41-BD3B-43C342634B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="-2100" windowWidth="28640" windowHeight="19400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="461">
   <si>
     <t>Status</t>
   </si>
@@ -71,9 +71,6 @@
     <t>Complete</t>
   </si>
   <si>
-    <t>Adrià López-Baucells albaucells@mcng.cat</t>
-  </si>
-  <si>
     <t>Vegetables (tomatos), Spain, Catalonia</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
     <t>Not tried - No use of acoustic bat lures known of</t>
   </si>
   <si>
-    <t>Alexandra Howard, alex.asterhof@gmail.com</t>
-  </si>
-  <si>
     <t>Apples, South Africa</t>
   </si>
   <si>
@@ -131,9 +125,6 @@
     <t>Tried, not tested - water sources have been created, but knowledge of its benefits to bats in this system is anecdotal or theoretical</t>
   </si>
   <si>
-    <t>Andrés Muñoz-Sáez, andrmunoz@uchile.cl</t>
-  </si>
-  <si>
     <t>Vineyards, Chile</t>
   </si>
   <si>
@@ -149,9 +140,6 @@
     <t>Not tried - No created/artificial habitats are known of</t>
   </si>
   <si>
-    <t>April Reside a.reside@uq.edu.au</t>
-  </si>
-  <si>
     <t>Lockyer Valley, QLD, Australia</t>
   </si>
   <si>
@@ -176,9 +164,6 @@
     <t>Did you guys try the lure in the Lockyer ever? or was that Sunshine Coast? do i remember that you tried it but nothing happened?</t>
   </si>
   <si>
-    <t>Ara Monadjem ara.monadjem@up.ac.za</t>
-  </si>
-  <si>
     <t>Sugar cane, Eswatini</t>
   </si>
   <si>
@@ -194,9 +179,6 @@
     <t>My PhD student, Siphesihle Magagula has been working closely with farm workers and school kids educating them about the importance of owls as predators of rodent pests. She has also incorporated bats in some of her talks, but as a side issue</t>
   </si>
   <si>
-    <t>Brooke Maslo, brooke.maslo@rutgers.edu</t>
-  </si>
-  <si>
     <t>pome fruits (apples, pears, peaches), New Jersey, USA</t>
   </si>
   <si>
@@ -215,9 +197,6 @@
     <t>I am unaware of acoustic lures being used here.</t>
   </si>
   <si>
-    <t>Carme Tuneu-Corral - email: tuneucorral@gmail.com</t>
-  </si>
-  <si>
     <t>Rice, Spain (Catalonia and Aragon regions).</t>
   </si>
   <si>
@@ -233,18 +212,12 @@
     <t>Is being tested in Catalonia, in vegetable plantations, but not close to rice paddies. water sources were created specifically to attract bats</t>
   </si>
   <si>
-    <t>Carme Tuneu-Corral - tuneucorral@gmail.com</t>
-  </si>
-  <si>
     <t>Rice, Madagascar</t>
   </si>
   <si>
     <t>Talks in schools and in broadcast in a radio program, designed to promote bat conservation</t>
   </si>
   <si>
-    <t>Carmi Korine, ckorine@bgu.ac.il</t>
-  </si>
-  <si>
     <t>olive</t>
   </si>
   <si>
@@ -359,9 +332,6 @@
     <t>Evidence that proximity to Mediterranean maquis affects positively and significantly bat activity (in preparation)</t>
   </si>
   <si>
-    <t>Cárol Sierra-Durán camsierradu@unal.edu.co</t>
-  </si>
-  <si>
     <t>Tomato, Extremadura, Spain.</t>
   </si>
   <si>
@@ -389,15 +359,9 @@
     <t>No revegetation programs for increasing landscape heterogeneity have been developed in the study area.</t>
   </si>
   <si>
-    <t>Carolina Ocampo carocampoa@gmail.com</t>
-  </si>
-  <si>
     <t>Cacao agroforestry, San Martin, Peru.</t>
   </si>
   <si>
-    <t>Cecilia Montauban - montauc50@gmail.com</t>
-  </si>
-  <si>
     <t>cacao - Ghana</t>
   </si>
   <si>
@@ -407,9 +371,6 @@
     <t>The project I am involved with has done outreach at a broader level - not with bats, but with biodiversity more generally. https://www.sentinel-gcrf.org/</t>
   </si>
   <si>
-    <t>Danilo Russo; danrusso@unina.it</t>
-  </si>
-  <si>
     <t>Tried and evaluated - There is confidence that agrochemical use has been reduced and the effect on bat activity or populations was measured</t>
   </si>
   <si>
@@ -422,9 +383,6 @@
     <t xml:space="preserve">The farm where we worked is a very special case. They have constant cooperation with zoologists and ecologists, and are very open to any action aimed at preserving biodiversity </t>
   </si>
   <si>
-    <t>Diogo Ferreira; ferreiradfa@gmail.com</t>
-  </si>
-  <si>
     <t>Cacao; Cameroon</t>
   </si>
   <si>
@@ -437,9 +395,6 @@
     <t>Our project had workshops developed to deliver the farmers the results of our project, showing the benefits of bats/birds and information on how to manage the farm to have higher diversity. However, there wasn't a follow-up</t>
   </si>
   <si>
-    <t>Dr. Kadambari Deshpande, Email: kadambari.deshpande@iihs.ac.in</t>
-  </si>
-  <si>
     <t>Rice-paddies, Karnataka, India</t>
   </si>
   <si>
@@ -452,9 +407,6 @@
     <t>I have conducted outreach activities with local farmers, key respondents, and planters in the region, through personal interactions, educational awareness creation through key stakeholders, and popular articles, to educate local people about bats, their ecosystem services and promoting their conservation. In the course of this work, I have observed mostly positive changes in their awareness levels, scientific information about bats, and perceptions and attitudes towards bats.</t>
   </si>
   <si>
-    <t>Elisa Fuentes-Montemayor &lt;elisa.fuentes-montemayor@stir.ac.uk&gt;</t>
-  </si>
-  <si>
     <t>A mixture of crops (mainly cereals + potatoes + brassicas) OR Pasture grassland with livestock (cattle and/or sheep) of for livestock feed OR Pasture grassland with livestock (cattle and/or sheep) of for livestock feed OR Mixed crop-livestock farming systems with livestock integrated into the crop rotation, either through rotation of temporary grassland and/or by grazing cover crops or herbal leys</t>
   </si>
   <si>
@@ -476,10 +428,6 @@
     <t>Not to my knowledge</t>
   </si>
   <si>
-    <t>Florence Matutini
- florence.matutini@ofb.gouv.fr</t>
-  </si>
-  <si>
     <t>Large-scale arable crops, mainly mosaics of wheat, barley, oilseed rape and maize grown in intensive farming systems</t>
   </si>
   <si>
@@ -489,9 +437,6 @@
     <t>The ponds were not specifically created for biodiversity, but for livestock. We are currently assessing their effect on bats and their interactions with hedgerows.</t>
   </si>
   <si>
-    <t>Gary McCracken</t>
-  </si>
-  <si>
     <t>Cotton, Texas</t>
   </si>
   <si>
@@ -519,9 +464,6 @@
     <t>Several videos have been produced.</t>
   </si>
   <si>
-    <t>Heidi Kolkert, hkolker2@une.edu.au</t>
-  </si>
-  <si>
     <t>cotton, Australia, Inland Northern NSW</t>
   </si>
   <si>
@@ -561,9 +503,6 @@
     <t xml:space="preserve">This is the first research into blueberries that I know of in Australia. This area has been particualy susceptable to environmental/soil and water damage due to large scale clearing for banana plantations - then later blueberries. Lots of forever chemicals detected in waterways.  There is nothing that specifically protects bats. Remnant corridors of woodland and planted woodland exist - as a part of the conditions of consent for development. Costa/Driscoll seem to be receptive to further biodiversity management but nothiing in place yet. Due to the large scale coporpation of Costa/Driscoll berries it was too hard to get permission to be on site at night to capture bats. </t>
   </si>
   <si>
-    <t>Hugo Rebelo herebelo@fc.ul.pt</t>
-  </si>
-  <si>
     <t>Several models of bat boxes placed, frequently using left overs from bat wine bottle crates.</t>
   </si>
   <si>
@@ -582,18 +521,12 @@
     <t>Two workshops and one participation on the assembly of common grounds was made.</t>
   </si>
   <si>
-    <t>Hui Wu wuh123@nenu.edu.cn</t>
-  </si>
-  <si>
     <t>apple in China</t>
   </si>
   <si>
     <t>Bat boxes tried</t>
   </si>
   <si>
-    <t>Jarod jarodmctaggart1312@gmail.com @jaja1312</t>
-  </si>
-  <si>
     <t>New Zealand</t>
   </si>
   <si>
@@ -607,9 +540,6 @@
   </si>
   <si>
     <t>Lots of natural water sources - may be some wetland but not sure</t>
-  </si>
-  <si>
-    <t>Jeremy Froidevaux : jeremy.froidevaux@univ-fcomte.fr</t>
   </si>
   <si>
     <t>Mixed farming (wheat &amp; corn algonside cow pastures) in the Jura Massif</t>
@@ -626,9 +556,6 @@
   </si>
   <si>
     <t>Many natural watercourses and ponds occur in the landscape and the benefits to bats are expected to be limited (although not tested!)</t>
-  </si>
-  <si>
-    <t>Jérémy Froidevaux : jeremy.froidevaux@univ-fcomte.fr</t>
   </si>
   <si>
     <t>Vineyard, France, South &amp; South-West of France</t>
@@ -655,27 +582,18 @@
     <t>Too risky at the moment as some recordings could deter bats.</t>
   </si>
   <si>
-    <t>Jian-Nan Liu</t>
-  </si>
-  <si>
     <t>Rice, Hualien County, Taiwan</t>
   </si>
   <si>
     <t>Our study tried to answer this question. We have some data but not published yet.</t>
   </si>
   <si>
-    <t>José M. Herrera josemanuel.herrera@uca.es</t>
-  </si>
-  <si>
     <t>Olive groves</t>
   </si>
   <si>
     <t>Workshops targeted to farmers and public audience</t>
   </si>
   <si>
-    <t xml:space="preserve">Leonardo Ancillotto leonardo.ancillotto@cnr.it </t>
-  </si>
-  <si>
     <t>Olives, Tuscany, Italy</t>
   </si>
   <si>
@@ -688,9 +606,6 @@
     <t>wooden flat-shaped bat boxes installed in rural buildings next to crops</t>
   </si>
   <si>
-    <t>Maggie Campbell-Jones mcampbelljones@usc.edu.au</t>
-  </si>
-  <si>
     <t>Cotton, Moree Plains, Australia</t>
   </si>
   <si>
@@ -707,9 +622,6 @@
   </si>
   <si>
     <t>Many artificial water sources- I don't think any have been developed for biodiversity benefit but certainly attract birds etc.</t>
-  </si>
-  <si>
-    <t>Nayelli Rivera, a.riveravillanueva@student.uq.edu.au</t>
   </si>
   <si>
     <t>corn, pumpkin, grape in Zacatecas, Mexico</t>
@@ -734,9 +646,6 @@
     <t>No bat lures have been tried or tested in the region.</t>
   </si>
   <si>
-    <t>Peter Taylor taylorpj@ufs.ac.za</t>
-  </si>
-  <si>
     <t>Litchees, South Africa</t>
   </si>
   <si>
@@ -752,9 +661,6 @@
     <t>Engagement with macadamia industry and farmers over a 10-year period, not current. My PhD student is now emploted in the sector.</t>
   </si>
   <si>
-    <t>Rani rani.davis@uq.net.au</t>
-  </si>
-  <si>
     <t xml:space="preserve">Macadamia. Australia, Southeast Queensland </t>
   </si>
   <si>
@@ -776,18 +682,12 @@
     <t>We have tried to use acoustic lures to improve capture rates on macadamia farns, but not to benefit pest control in any way. Just to attract the bats to the trap</t>
   </si>
   <si>
-    <t>Sándor Zsebők zsebok.s@gmail.com</t>
-  </si>
-  <si>
     <t>vineyard, Hungary</t>
   </si>
   <si>
     <t>Reduced agrochemical use has been evaluated in Hungarian vineyards by comparing organic and integrated pest management (IPM) systems. Organic vineyards were managed without synthetic insecticides, herbicides, or fertilizers, and bat activity was monitored using acoustic surveys. The study found no significant direct effect of vineyard management (organic versus IPM) on bat activity, suggesting that landscape features such as forest cover and habitat connectivity may be more important drivers of bat occurrence than local pesticide-use intensity. Nevertheless, the effects of reduced agrochemical use on bats have been explicitly tested in this system.</t>
   </si>
   <si>
-    <t>Siteri Tikoca- stikoca@gmail.com</t>
-  </si>
-  <si>
     <t>Sugar cane, mixed plantations, coconut groves, mixed forest, &amp; good forest.</t>
   </si>
   <si>
@@ -809,9 +709,6 @@
     <t>No</t>
   </si>
   <si>
-    <t>Stuart Parsons (stuart.parsons@canterbury.ac.nz)</t>
-  </si>
-  <si>
     <t>Cotton, bassicas, maize</t>
   </si>
   <si>
@@ -833,9 +730,6 @@
     <t>Use of acoustic lures controlled in some countries for birds (ethics) so need to be aware of this happening for bats.</t>
   </si>
   <si>
-    <t>Teja Tscharntke, ttschar@gwdg.de</t>
-  </si>
-  <si>
     <t>Kakao, Peru (near Piura)</t>
   </si>
   <si>
@@ -857,16 +751,9 @@
     <t>Landscape context (forst distance) measured</t>
   </si>
   <si>
-    <t>Tinglei Jiang</t>
-  </si>
-  <si>
     <t>Corn in China</t>
   </si>
   <si>
-    <t>Xavier Puig-Montserrat
-xavier.puig@uvic.cat</t>
-  </si>
-  <si>
     <t>Olive groves, Spain, Catalonia</t>
   </si>
   <si>
@@ -909,9 +796,6 @@
     <t xml:space="preserve">Extensive dissemination efforts have been conducted in the region to transfer the current knowledge on the regulatory ecosystem services bats provide. Videos and guidelines to enhance biodiversity in vineyards have been produced. </t>
   </si>
   <si>
-    <t>Zenon Czenze, zczenze@une.edu.au; Heidi Kolkert &lt;hkolker2@une.edu.au&gt;</t>
-  </si>
-  <si>
     <t>Wine Grapes, NSW/Vic, Australia</t>
   </si>
   <si>
@@ -933,21 +817,6 @@
     <t>Incomplete</t>
   </si>
   <si>
-    <t>Helen Taylor-Boyd; batsinzambia@gmail.com</t>
-  </si>
-  <si>
-    <t>Yingying Liu; liuyy777@nenu.edu.cn</t>
-  </si>
-  <si>
-    <t>Bea Maas bea.maas@univie.ac.at</t>
-  </si>
-  <si>
-    <t>Olga Heim bats@o-heim.de &lt;bats@o-heim.de&gt;</t>
-  </si>
-  <si>
-    <t>Dr Kirsten Reichel-Jung kirsten.jung@uni-ulm.de</t>
-  </si>
-  <si>
     <t>Respondent.clean</t>
   </si>
   <si>
@@ -1401,9 +1270,6 @@
     <t>Multi-region: New South Wales &amp; Victoria</t>
   </si>
   <si>
-    <t>Chiara Paniccia &lt;chiara.paniccia@eurac.edu&gt;</t>
-  </si>
-  <si>
     <t>R39</t>
   </si>
   <si>
@@ -1428,9 +1294,6 @@
     <t>AH</t>
   </si>
   <si>
-    <t>AS</t>
-  </si>
-  <si>
     <t>AR</t>
   </si>
   <si>
@@ -1543,6 +1406,9 @@
   </si>
   <si>
     <t>CP</t>
+  </si>
+  <si>
+    <t>AMS</t>
   </si>
 </sst>
 </file>
@@ -2598,28 +2464,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>306</v>
+        <v>263</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>307</v>
+        <v>264</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>309</v>
+        <v>266</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>310</v>
+        <v>267</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>311</v>
+        <v>268</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>312</v>
+        <v>269</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>313</v>
+        <v>270</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>1</v>
@@ -2669,67 +2535,67 @@
         <v>15</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>464</v>
+        <v>420</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>314</v>
+        <v>271</v>
       </c>
       <c r="D2" s="7">
         <v>1</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>315</v>
+        <v>272</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>316</v>
+        <v>273</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>318</v>
+        <v>275</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="J2" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="O2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="Q2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="R2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="S2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="T2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="U2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="V2" s="9" t="s">
         <v>27</v>
-      </c>
-      <c r="V2" s="9" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2737,55 +2603,55 @@
         <v>15</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>465</v>
+        <v>421</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>320</v>
+        <v>277</v>
       </c>
       <c r="D3" s="8">
         <v>1</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>321</v>
+        <v>278</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>322</v>
+        <v>279</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J3" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="N3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="P3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="R3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="R3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="T3" s="9" t="s">
-        <v>35</v>
-      </c>
       <c r="V3" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2793,58 +2659,58 @@
         <v>15</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>325</v>
+        <v>282</v>
       </c>
       <c r="D4" s="8">
         <v>1</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>326</v>
+        <v>283</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>327</v>
+        <v>284</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>328</v>
+        <v>285</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="J4" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="R4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4" s="9" t="s">
+      <c r="T4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="T4" s="9" t="s">
-        <v>41</v>
-      </c>
       <c r="V4" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2852,70 +2718,70 @@
         <v>15</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>467</v>
+        <v>422</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>330</v>
+        <v>287</v>
       </c>
       <c r="D5" s="8">
         <v>1</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>331</v>
+        <v>288</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>334</v>
+        <v>291</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="J5" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="R5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="9" t="s">
+      <c r="T5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="U5" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="N5" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="O5" s="9" t="s">
+      <c r="V5" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="P5" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q5" s="9" t="s">
+      <c r="W5" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="R5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="S5" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="T5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="U5" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="V5" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="W5" s="9" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2923,61 +2789,61 @@
         <v>15</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>468</v>
+        <v>423</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>336</v>
+        <v>293</v>
       </c>
       <c r="D6" s="8">
         <v>1</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>337</v>
+        <v>294</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>338</v>
+        <v>295</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>339</v>
+        <v>296</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="J6" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="S6" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="K6" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="P6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q6" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="R6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="S6" s="9" t="s">
-        <v>56</v>
-      </c>
       <c r="T6" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V6" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2985,67 +2851,67 @@
         <v>15</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>469</v>
+        <v>424</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>341</v>
+        <v>298</v>
       </c>
       <c r="D7" s="8">
         <v>1</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>342</v>
+        <v>299</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>344</v>
+        <v>301</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>345</v>
+        <v>302</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J7" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="V7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="R7" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="S7" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="T7" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="V7" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="W7" s="9" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3053,61 +2919,61 @@
         <v>15</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>470</v>
+        <v>425</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="D8" s="8">
         <v>2</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>347</v>
+        <v>304</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>316</v>
+        <v>273</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>348</v>
+        <v>305</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>64</v>
+        <v>306</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>425</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P8" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R8" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S8" s="9" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="V8" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3115,55 +2981,55 @@
         <v>15</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>470</v>
+        <v>425</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="D9" s="8">
         <v>1</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>350</v>
+        <v>307</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>351</v>
+        <v>308</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>348</v>
+        <v>305</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>70</v>
+        <v>306</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>425</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P9" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R9" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S9" s="9" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V9" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3171,55 +3037,55 @@
         <v>15</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="D10" s="8">
         <v>9</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>73</v>
+        <v>281</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R10" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V10" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3227,67 +3093,67 @@
         <v>15</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="D11" s="8">
         <v>1</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>356</v>
+        <v>313</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>357</v>
+        <v>314</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J11" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="S11" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K11" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="R11" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="S11" s="9" t="s">
-        <v>82</v>
-      </c>
       <c r="T11" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3295,64 +3161,64 @@
         <v>15</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>359</v>
+        <v>316</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>358</v>
+        <v>315</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>73</v>
+        <v>281</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N12" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T12" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="U12" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="O12" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="R12" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="S12" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="T12" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="U12" s="9" t="s">
-        <v>87</v>
-      </c>
       <c r="V12" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W12" s="9" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3360,67 +3226,67 @@
         <v>15</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>360</v>
+        <v>317</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>361</v>
+        <v>318</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>73</v>
+        <v>297</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R13" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="V13" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W13" s="9" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3428,64 +3294,64 @@
         <v>15</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>363</v>
+        <v>320</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>362</v>
+        <v>319</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>73</v>
+        <v>286</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="P14" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R14" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S14" s="9" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U14" s="9" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="V14" s="9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="W14" s="9" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3493,55 +3359,55 @@
         <v>15</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>363</v>
+        <v>320</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>362</v>
+        <v>319</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>73</v>
+        <v>286</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R15" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V15" s="9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3549,64 +3415,64 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="D16" s="8">
         <v>21</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>356</v>
+        <v>313</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>364</v>
+        <v>321</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>73</v>
+        <v>276</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P16" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R16" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U16" s="9" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="V16" s="9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="W16" s="9" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3614,64 +3480,64 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="D17" s="8">
         <v>2</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>356</v>
+        <v>313</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>73</v>
+        <v>276</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S17" s="9" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U17" s="9" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="V17" s="9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="W17" s="9" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3679,67 +3545,67 @@
         <v>15</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="D18" s="8">
         <v>16</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>366</v>
+        <v>323</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>365</v>
+        <v>322</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>73</v>
+        <v>276</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="P18" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R18" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S18" s="9" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U18" s="9" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="V18" s="9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="W18" s="9" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3747,70 +3613,70 @@
         <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="D19" s="8">
         <v>3</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>356</v>
+        <v>313</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>73</v>
+        <v>276</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="R19" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U19" s="9" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="V19" s="9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="W19" s="9" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3818,55 +3684,55 @@
         <v>15</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>363</v>
+        <v>320</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>362</v>
+        <v>319</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>73</v>
+        <v>286</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="P20" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="R20" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3874,61 +3740,61 @@
         <v>15</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>472</v>
+        <v>427</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>367</v>
+        <v>324</v>
       </c>
       <c r="D21" s="8">
         <v>2</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>368</v>
+        <v>325</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>316</v>
+        <v>273</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>318</v>
+        <v>275</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>112</v>
+        <v>276</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="R21" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V21" s="9" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3936,61 +3802,61 @@
         <v>15</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>472</v>
+        <v>427</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>367</v>
+        <v>324</v>
       </c>
       <c r="D22" s="8">
         <v>1</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>369</v>
+        <v>326</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>370</v>
+        <v>327</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>328</v>
+        <v>285</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>334</v>
+        <v>291</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>112</v>
+        <v>292</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="P22" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="R22" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V22" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3998,52 +3864,52 @@
         <v>15</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>473</v>
+        <v>428</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>371</v>
+        <v>328</v>
       </c>
       <c r="D23" s="8">
         <v>1</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>372</v>
+        <v>329</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>373</v>
+        <v>330</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>328</v>
+        <v>285</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>374</v>
+        <v>331</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>122</v>
+        <v>331</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>428</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R23" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V23" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4051,58 +3917,58 @@
         <v>15</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>474</v>
+        <v>429</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>375</v>
+        <v>332</v>
       </c>
       <c r="D24" s="8">
         <v>1</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>376</v>
+        <v>333</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>377</v>
+        <v>334</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>378</v>
+        <v>335</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>124</v>
+        <v>292</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>429</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="P24" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R24" s="9" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V24" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4110,55 +3976,55 @@
         <v>15</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>475</v>
+        <v>430</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>379</v>
+        <v>336</v>
       </c>
       <c r="D25" s="8">
         <v>1</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>380</v>
+        <v>337</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>128</v>
+        <v>281</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>430</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R25" s="9" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V25" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4166,61 +4032,61 @@
         <v>15</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>476</v>
+        <v>431</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>382</v>
+        <v>339</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>385</v>
+        <v>342</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>383</v>
+        <v>340</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>384</v>
+        <v>341</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>374</v>
+        <v>331</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>133</v>
+        <v>331</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>431</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P26" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="R26" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V26" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4228,61 +4094,61 @@
         <v>15</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>477</v>
+        <v>432</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>386</v>
+        <v>343</v>
       </c>
       <c r="D27" s="8">
         <v>1</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>387</v>
+        <v>344</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>388</v>
+        <v>345</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>389</v>
+        <v>346</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>348</v>
+        <v>305</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>138</v>
+        <v>306</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>432</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R27" s="9" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="S27" s="9" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V27" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4290,70 +4156,70 @@
         <v>15</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>478</v>
+        <v>433</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>390</v>
+        <v>347</v>
       </c>
       <c r="D28" s="7">
         <v>3</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>391</v>
+        <v>348</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>392</v>
+        <v>349</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>393</v>
+        <v>350</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>143</v>
+        <v>292</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>433</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O28" s="9" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="P28" s="9" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="R28" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U28" s="9" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="V28" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W28" s="9" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4361,52 +4227,52 @@
         <v>15</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>479</v>
+        <v>434</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>394</v>
+        <v>351</v>
       </c>
       <c r="D29" s="7">
         <v>1</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>395</v>
+        <v>352</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>396</v>
+        <v>353</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>393</v>
+        <v>350</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>151</v>
+        <v>292</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>434</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="R29" s="9" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V29" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4414,55 +4280,55 @@
         <v>15</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>479</v>
+        <v>434</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>394</v>
+        <v>351</v>
       </c>
       <c r="D30" s="7">
         <v>2</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>395</v>
+        <v>352</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>396</v>
+        <v>353</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>393</v>
+        <v>350</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>151</v>
+        <v>292</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>434</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P30" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R30" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U30" s="9" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="V30" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4470,52 +4336,52 @@
         <v>15</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>479</v>
+        <v>434</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>394</v>
+        <v>351</v>
       </c>
       <c r="D31" s="7">
         <v>3</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>397</v>
+        <v>354</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>396</v>
+        <v>353</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>151</v>
+        <v>281</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>434</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R31" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V31" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4523,64 +4389,64 @@
         <v>15</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>480</v>
+        <v>435</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>398</v>
+        <v>355</v>
       </c>
       <c r="D32" s="7">
         <v>1</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>399</v>
+        <v>356</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>344</v>
+        <v>301</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>155</v>
+        <v>297</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>435</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="M32" s="9" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O32" s="9" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="P32" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R32" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S32" s="9" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V32" s="9" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="W32" s="9" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4588,61 +4454,61 @@
         <v>15</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>480</v>
+        <v>435</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>398</v>
+        <v>355</v>
       </c>
       <c r="D33" s="7">
         <v>2</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>400</v>
+        <v>357</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>344</v>
+        <v>301</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>401</v>
+        <v>358</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>155</v>
+        <v>281</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>435</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="M33" s="9" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R33" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S33" s="9" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V33" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4650,67 +4516,67 @@
         <v>15</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>481</v>
+        <v>436</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>402</v>
+        <v>359</v>
       </c>
       <c r="D34" s="8">
         <v>1</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>403</v>
+        <v>360</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>165</v>
+        <v>297</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>436</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M34" s="9" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="P34" s="9" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="R34" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S34" s="9" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U34" s="9" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="V34" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4718,70 +4584,70 @@
         <v>15</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>481</v>
+        <v>436</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>402</v>
+        <v>359</v>
       </c>
       <c r="D35" s="8">
         <v>2</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>403</v>
+        <v>360</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>404</v>
+        <v>361</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>165</v>
+        <v>281</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>436</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M35" s="9" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="R35" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S35" s="9" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U35" s="9" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="V35" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W35" s="9" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4789,64 +4655,64 @@
         <v>15</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>482</v>
+        <v>437</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>405</v>
+        <v>362</v>
       </c>
       <c r="D36" s="7">
         <v>1</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>406</v>
+        <v>363</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>407</v>
+        <v>364</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>179</v>
+        <v>286</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>437</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="N36" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="P36" s="9" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="R36" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S36" s="9" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="T36" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U36" s="9" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="V36" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4854,55 +4720,55 @@
         <v>15</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>482</v>
+        <v>437</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>405</v>
+        <v>362</v>
       </c>
       <c r="D37" s="7">
         <v>2</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>408</v>
+        <v>365</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>407</v>
+        <v>364</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>409</v>
+        <v>366</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>179</v>
+        <v>367</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>437</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R37" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S37" s="9" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="T37" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V37" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4910,55 +4776,55 @@
         <v>15</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>483</v>
+        <v>438</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>411</v>
+        <v>368</v>
       </c>
       <c r="D38" s="8">
         <v>1</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>412</v>
+        <v>369</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>413</v>
+        <v>370</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>414</v>
+        <v>371</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>186</v>
+        <v>281</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>438</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="N38" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P38" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R38" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="T38" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V38" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4966,64 +4832,64 @@
         <v>15</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>484</v>
+        <v>439</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>415</v>
+        <v>372</v>
       </c>
       <c r="D39" s="8">
         <v>1</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>416</v>
+        <v>373</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>393</v>
+        <v>350</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>189</v>
+        <v>292</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>439</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="R39" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="S39" s="9" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="T39" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U39" s="9" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="V39" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5031,61 +4897,61 @@
         <v>15</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>485</v>
+        <v>440</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>417</v>
+        <v>374</v>
       </c>
       <c r="D40" s="8">
         <v>1</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>418</v>
+        <v>375</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>396</v>
+        <v>353</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>393</v>
+        <v>350</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>195</v>
+        <v>292</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>440</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N40" s="9" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="P40" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="R40" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="S40" s="9" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="T40" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U40" s="9" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="V40" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5093,70 +4959,70 @@
         <v>15</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>485</v>
+        <v>440</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>419</v>
+        <v>376</v>
       </c>
       <c r="D41" s="8">
         <v>2</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>420</v>
+        <v>377</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>396</v>
+        <v>353</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="J41" s="9" t="s">
-        <v>201</v>
+        <v>286</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>440</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="L41" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="R41" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S41" s="9" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="T41" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U41" s="9" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="V41" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W41" s="9" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5164,55 +5030,55 @@
         <v>15</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>486</v>
+        <v>441</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>421</v>
+        <v>378</v>
       </c>
       <c r="D42" s="8">
         <v>1</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>422</v>
+        <v>379</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>423</v>
+        <v>380</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>414</v>
+        <v>371</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>348</v>
+        <v>305</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>209</v>
+        <v>306</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>441</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O42" s="9" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="P42" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R42" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="T42" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V42" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5220,55 +5086,55 @@
         <v>15</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>487</v>
+        <v>442</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>424</v>
+        <v>381</v>
       </c>
       <c r="D43" s="7">
         <v>1</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>406</v>
+        <v>363</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>407</v>
+        <v>364</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>212</v>
+        <v>281</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>442</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="L43" s="9" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="R43" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S43" s="9" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="T43" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V43" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5276,55 +5142,55 @@
         <v>15</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>488</v>
+        <v>443</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>425</v>
+        <v>382</v>
       </c>
       <c r="D44" s="7">
         <v>1</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>426</v>
+        <v>383</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J44" s="9" t="s">
-        <v>215</v>
+        <v>281</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>443</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O44" s="9" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="P44" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R44" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T44" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V44" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5332,55 +5198,55 @@
         <v>15</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>488</v>
+        <v>443</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>425</v>
+        <v>382</v>
       </c>
       <c r="D45" s="7">
         <v>2</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>427</v>
+        <v>384</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>334</v>
+        <v>291</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>215</v>
+        <v>292</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>443</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R45" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T45" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V45" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5388,67 +5254,67 @@
         <v>15</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>489</v>
+        <v>444</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>428</v>
+        <v>385</v>
       </c>
       <c r="D46" s="8">
         <v>1</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>403</v>
+        <v>360</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="J46" s="9" t="s">
-        <v>220</v>
+        <v>297</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>444</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="L46" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="N46" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O46" s="9" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="P46" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q46" s="9" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="R46" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S46" s="9" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="T46" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U46" s="9" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="V46" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5456,70 +5322,70 @@
         <v>15</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>490</v>
+        <v>445</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>429</v>
+        <v>386</v>
       </c>
       <c r="D47" s="8">
         <v>1</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>430</v>
+        <v>387</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>370</v>
+        <v>327</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>328</v>
+        <v>285</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>378</v>
+        <v>335</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>227</v>
+        <v>292</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>445</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="L47" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M47" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="N47" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="M47" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="N47" s="9" t="s">
-        <v>33</v>
-      </c>
       <c r="O47" s="9" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="R47" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S47" s="9" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="T47" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U47" s="9" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="V47" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W47" s="9" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5527,52 +5393,52 @@
         <v>15</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>491</v>
+        <v>446</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>431</v>
+        <v>388</v>
       </c>
       <c r="D48" s="8">
         <v>1</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>432</v>
+        <v>389</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>322</v>
+        <v>279</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>433</v>
+        <v>390</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J48" s="9" t="s">
-        <v>235</v>
+        <v>281</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>446</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="L48" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N48" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="N48" s="9" t="s">
-        <v>33</v>
-      </c>
       <c r="P48" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R48" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T48" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V48" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5580,61 +5446,61 @@
         <v>15</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>491</v>
+        <v>446</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>431</v>
+        <v>388</v>
       </c>
       <c r="D49" s="8">
         <v>2</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>432</v>
+        <v>389</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>322</v>
+        <v>279</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>434</v>
+        <v>391</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J49" s="9" t="s">
-        <v>235</v>
+        <v>281</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>446</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R49" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S49" s="9" t="s">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="T49" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V49" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5642,70 +5508,70 @@
         <v>15</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>492</v>
+        <v>447</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>435</v>
+        <v>392</v>
       </c>
       <c r="D50" s="8">
         <v>1</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>331</v>
+        <v>288</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>434</v>
+        <v>391</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J50" s="9" t="s">
-        <v>241</v>
+        <v>281</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>447</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M50" s="9" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="N50" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O50" s="9" t="s">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="P50" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q50" s="9" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="R50" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S50" s="9" t="s">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="T50" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U50" s="9" t="s">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="V50" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W50" s="9" t="s">
-        <v>248</v>
+        <v>217</v>
       </c>
     </row>
     <row r="51" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5713,55 +5579,55 @@
         <v>15</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>493</v>
+        <v>448</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>436</v>
+        <v>393</v>
       </c>
       <c r="D51" s="7">
         <v>1</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>437</v>
+        <v>394</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>438</v>
+        <v>395</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="J51" s="9" t="s">
-        <v>249</v>
+        <v>286</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>448</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="L51" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R51" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="T51" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V51" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5769,70 +5635,70 @@
         <v>15</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>494</v>
+        <v>449</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>439</v>
+        <v>396</v>
       </c>
       <c r="D52" s="8">
         <v>1</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>440</v>
+        <v>397</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>441</v>
+        <v>398</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>378</v>
+        <v>335</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="J52" s="9" t="s">
-        <v>252</v>
+        <v>292</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>449</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="L52" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="N52" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O52" s="9" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="P52" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q52" s="9" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="R52" s="9" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="S52" s="9" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="T52" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U52" s="9" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="V52" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W52" s="9" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
     </row>
     <row r="53" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5840,70 +5706,70 @@
         <v>15</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>495</v>
+        <v>450</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>442</v>
+        <v>399</v>
       </c>
       <c r="D53" s="8">
         <v>1</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>443</v>
+        <v>400</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>444</v>
+        <v>401</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>378</v>
+        <v>335</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="J53" s="9" t="s">
-        <v>260</v>
+        <v>292</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>450</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>261</v>
+        <v>227</v>
       </c>
       <c r="L53" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>262</v>
+        <v>228</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>263</v>
+        <v>229</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q53" s="9" t="s">
-        <v>264</v>
+        <v>230</v>
       </c>
       <c r="R53" s="9" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="S53" s="9" t="s">
-        <v>265</v>
+        <v>231</v>
       </c>
       <c r="T53" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U53" s="9" t="s">
-        <v>266</v>
+        <v>232</v>
       </c>
       <c r="V53" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W53" s="9" t="s">
-        <v>267</v>
+        <v>233</v>
       </c>
     </row>
     <row r="54" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5911,61 +5777,61 @@
         <v>15</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>496</v>
+        <v>451</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>445</v>
+        <v>402</v>
       </c>
       <c r="D54" s="8">
         <v>2</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>450</v>
+        <v>407</v>
       </c>
       <c r="F54" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="J54" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="G54" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="J54" s="9" t="s">
-        <v>268</v>
-      </c>
       <c r="K54" s="9" t="s">
-        <v>269</v>
+        <v>234</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N54" s="9" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="O54" s="9" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="P54" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q54" s="9" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
       <c r="R54" s="9" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="S54" s="9" t="s">
-        <v>272</v>
+        <v>237</v>
       </c>
       <c r="T54" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V54" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -5973,52 +5839,52 @@
         <v>15</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>496</v>
+        <v>451</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>445</v>
+        <v>402</v>
       </c>
       <c r="D55" s="8">
         <v>3</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>449</v>
+        <v>406</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>322</v>
+        <v>279</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>434</v>
+        <v>391</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J55" s="9" t="s">
-        <v>268</v>
+        <v>281</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>451</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>273</v>
+        <v>238</v>
       </c>
       <c r="L55" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N55" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="N55" s="9" t="s">
-        <v>33</v>
-      </c>
       <c r="P55" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R55" s="9" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="T55" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V55" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6026,55 +5892,55 @@
         <v>15</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>496</v>
+        <v>451</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>445</v>
+        <v>402</v>
       </c>
       <c r="D56" s="8">
         <v>1</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>446</v>
+        <v>403</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>447</v>
+        <v>404</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>448</v>
+        <v>405</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>374</v>
+        <v>331</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="J56" s="9" t="s">
-        <v>268</v>
+        <v>331</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>451</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N56" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P56" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q56" s="9" t="s">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="R56" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T56" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V56" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6082,52 +5948,52 @@
         <v>15</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>497</v>
+        <v>452</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>452</v>
+        <v>409</v>
       </c>
       <c r="D57" s="8">
         <v>1</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>453</v>
+        <v>410</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>413</v>
+        <v>370</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>414</v>
+        <v>371</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>378</v>
+        <v>335</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="J57" s="9" t="s">
-        <v>276</v>
+        <v>292</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>452</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
       <c r="L57" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N57" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P57" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R57" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="T57" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="P57" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="R57" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="T57" s="9" t="s">
-        <v>35</v>
-      </c>
       <c r="V57" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6135,64 +6001,64 @@
         <v>15</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>498</v>
+        <v>453</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>454</v>
+        <v>411</v>
       </c>
       <c r="D58" s="7">
         <v>1</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>315</v>
+        <v>272</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>316</v>
+        <v>273</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>453</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>279</v>
+        <v>242</v>
       </c>
       <c r="L58" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="N58" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O58" s="9" t="s">
-        <v>281</v>
+        <v>244</v>
       </c>
       <c r="P58" s="9" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="Q58" s="9" t="s">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="R58" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S58" s="9" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="T58" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V58" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6200,64 +6066,64 @@
         <v>15</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>498</v>
+        <v>453</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>454</v>
+        <v>411</v>
       </c>
       <c r="D59" s="7">
         <v>2</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>315</v>
+        <v>272</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>316</v>
+        <v>273</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>348</v>
+        <v>305</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>278</v>
+        <v>306</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>453</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="L59" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>285</v>
+        <v>248</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>286</v>
+        <v>249</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q59" s="9" t="s">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="R59" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S59" s="9" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="T59" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V59" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6265,64 +6131,64 @@
         <v>15</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>498</v>
+        <v>453</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>454</v>
+        <v>411</v>
       </c>
       <c r="D60" s="7">
         <v>3</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>315</v>
+        <v>272</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>316</v>
+        <v>273</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>453</v>
       </c>
       <c r="K60" s="9" t="s">
-        <v>288</v>
+        <v>251</v>
       </c>
       <c r="L60" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>289</v>
+        <v>252</v>
       </c>
       <c r="N60" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O60" s="9" t="s">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c r="P60" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q60" s="9" t="s">
-        <v>291</v>
+        <v>254</v>
       </c>
       <c r="R60" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S60" s="9" t="s">
-        <v>292</v>
+        <v>255</v>
       </c>
       <c r="T60" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V60" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6330,78 +6196,78 @@
         <v>15</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>499</v>
+        <v>454</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>455</v>
+        <v>412</v>
       </c>
       <c r="D61" s="14">
         <v>1</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>456</v>
+        <v>413</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="J61" s="9" t="s">
-        <v>293</v>
+        <v>286</v>
+      </c>
+      <c r="J61" s="13" t="s">
+        <v>454</v>
       </c>
       <c r="K61" s="9" t="s">
-        <v>294</v>
+        <v>256</v>
       </c>
       <c r="L61" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q61" s="9" t="s">
-        <v>297</v>
+        <v>259</v>
       </c>
       <c r="R61" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S61" s="9" t="s">
-        <v>298</v>
+        <v>260</v>
       </c>
       <c r="T61" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U61" s="9" t="s">
-        <v>299</v>
+        <v>261</v>
       </c>
       <c r="V61" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>500</v>
+        <v>455</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>458</v>
+        <v>414</v>
       </c>
       <c r="D62" s="17"/>
       <c r="E62" s="16"/>
@@ -6409,8 +6275,8 @@
       <c r="G62" s="16"/>
       <c r="H62" s="16"/>
       <c r="I62" s="16"/>
-      <c r="J62" s="15" t="s">
-        <v>301</v>
+      <c r="J62" s="20" t="s">
+        <v>455</v>
       </c>
       <c r="K62" s="15"/>
       <c r="L62" s="15"/>
@@ -6427,13 +6293,13 @@
     </row>
     <row r="63" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="21" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>501</v>
+        <v>456</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>459</v>
+        <v>415</v>
       </c>
       <c r="D63" s="17"/>
       <c r="E63" s="16"/>
@@ -6441,8 +6307,8 @@
       <c r="G63" s="16"/>
       <c r="H63" s="16"/>
       <c r="I63" s="16"/>
-      <c r="J63" s="15" t="s">
-        <v>302</v>
+      <c r="J63" s="12" t="s">
+        <v>456</v>
       </c>
       <c r="K63" s="15"/>
       <c r="L63" s="15"/>
@@ -6454,22 +6320,22 @@
       <c r="R63" s="15"/>
       <c r="S63" s="15"/>
       <c r="T63" s="15" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U63" s="15"/>
       <c r="V63" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="21" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>469</v>
+        <v>424</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="D64" s="17"/>
       <c r="E64" s="16"/>
@@ -6477,8 +6343,8 @@
       <c r="G64" s="16"/>
       <c r="H64" s="16"/>
       <c r="I64" s="16"/>
-      <c r="J64" s="15" t="s">
-        <v>303</v>
+      <c r="J64" s="12" t="s">
+        <v>424</v>
       </c>
       <c r="K64" s="15"/>
       <c r="L64" s="15"/>
@@ -6495,13 +6361,13 @@
     </row>
     <row r="65" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="21" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>502</v>
+        <v>457</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="D65" s="17"/>
       <c r="E65" s="16"/>
@@ -6509,8 +6375,8 @@
       <c r="G65" s="16"/>
       <c r="H65" s="16"/>
       <c r="I65" s="16"/>
-      <c r="J65" s="15" t="s">
-        <v>304</v>
+      <c r="J65" s="12" t="s">
+        <v>457</v>
       </c>
       <c r="K65" s="15"/>
       <c r="L65" s="15"/>
@@ -6527,13 +6393,13 @@
     </row>
     <row r="66" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="22" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>503</v>
+        <v>458</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>462</v>
+        <v>418</v>
       </c>
       <c r="D66" s="17"/>
       <c r="E66" s="16"/>
@@ -6541,8 +6407,8 @@
       <c r="G66" s="16"/>
       <c r="H66" s="16"/>
       <c r="I66" s="16"/>
-      <c r="J66" s="15" t="s">
-        <v>305</v>
+      <c r="J66" s="23" t="s">
+        <v>458</v>
       </c>
       <c r="K66" s="15"/>
       <c r="L66" s="15"/>
@@ -6559,16 +6425,16 @@
     </row>
     <row r="67" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="18" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>504</v>
+        <v>459</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="J67" s="18" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
